--- a/Cảm biến + Sim.xlsx
+++ b/Cảm biến + Sim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/43e69fe3b798304f/Work/PIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_F25DC773A252ABDACC104887E15F42345ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7A00BAB-7FDB-4A7E-973E-B13E6CFBF0B0}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_F25DC773A252ABDACC104887E15F42345ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6725E891-BFAE-4234-9FBD-23A11DF777FE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="5868" windowWidth="22332" windowHeight="10632" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>Zero</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>01698049699</t>
+  </si>
+  <si>
+    <t>BK1</t>
   </si>
 </sst>
 </file>
@@ -249,8 +252,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Siêu kết nối" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -263,6 +266,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -661,6 +668,9 @@
       <c r="E6" s="3">
         <v>45865</v>
       </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">

--- a/Cảm biến + Sim.xlsx
+++ b/Cảm biến + Sim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/43e69fe3b798304f/Work/PIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_F25DC773A252ABDACC104887E15F42345ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6725E891-BFAE-4234-9FBD-23A11DF777FE}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_F25DC773A252ABDACC104887E15F42345ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B63D6255-6C2C-4CBD-A136-B91A8B6B4C09}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="5868" windowWidth="22332" windowHeight="10632" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>Zero</t>
   </si>
@@ -88,9 +88,6 @@
     <t>01699517089</t>
   </si>
   <si>
-    <t>Bờ kè 4</t>
-  </si>
-  <si>
     <t>01699516205</t>
   </si>
   <si>
@@ -158,9 +155,6 @@
   </si>
   <si>
     <t>01698049699</t>
-  </si>
-  <si>
-    <t>BK1</t>
   </si>
 </sst>
 </file>
@@ -200,12 +194,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -236,7 +236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -250,6 +250,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -266,10 +277,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,28 +663,28 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3">
-        <v>45865</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46629</v>
+      </c>
+      <c r="F6" s="11">
+        <v>20000</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -688,10 +695,10 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -702,10 +709,10 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -716,10 +723,10 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -730,18 +737,18 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -750,15 +757,15 @@
         <v>46374</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -767,15 +774,15 @@
         <v>46374</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -786,10 +793,10 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>11</v>
@@ -798,12 +805,12 @@
         <v>46588</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C17" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
